--- a/Excel/Revisão geral.xlsx
+++ b/Excel/Revisão geral.xlsx
@@ -1,25 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Aulas\1. Aplicativos Informatizados - Mecânica\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Aulas\7. Aplicativos informatizados - Administração - 232\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{00B54315-D065-4511-B488-18D25F0B0A0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86F7BECD-3234-4A67-8BDD-1549FCBC6F88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="770" activeTab="6" xr2:uid="{9215DF5D-1876-4B09-AE63-57FB0E85D20A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="770" xr2:uid="{9215DF5D-1876-4B09-AE63-57FB0E85D20A}"/>
   </bookViews>
   <sheets>
     <sheet name="Introdução" sheetId="2" r:id="rId1"/>
-    <sheet name="Desafio" sheetId="3" r:id="rId2"/>
-    <sheet name="Op. Matemáticos" sheetId="4" r:id="rId3"/>
-    <sheet name="Op. Relacionais" sheetId="5" r:id="rId4"/>
-    <sheet name="Porcentagens" sheetId="7" r:id="rId5"/>
-    <sheet name="Exponenciação" sheetId="8" r:id="rId6"/>
-    <sheet name="Tabela_periódica" sheetId="1" r:id="rId7"/>
+    <sheet name="Tabela_periódica" sheetId="1" r:id="rId2"/>
+    <sheet name="Desafio" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="99">
   <si>
     <t>Operadores de cálculo e ordem de execução</t>
   </si>
@@ -245,12 +241,6 @@
     <t>Data de nascimento</t>
   </si>
   <si>
-    <t>Descontos</t>
-  </si>
-  <si>
-    <t>Brinde</t>
-  </si>
-  <si>
     <t>Sexo</t>
   </si>
   <si>
@@ -320,106 +310,31 @@
     <t>Modo 2</t>
   </si>
   <si>
-    <t>Valor 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Valor 2</t>
-  </si>
-  <si>
-    <t>Resultado</t>
-  </si>
-  <si>
-    <t>Valor 2</t>
-  </si>
-  <si>
-    <t>Porcentagem</t>
-  </si>
-  <si>
-    <t>%</t>
-  </si>
-  <si>
-    <t>Por 100</t>
-  </si>
-  <si>
-    <t>Divisão de qualquer coisa em 100 partes iguais</t>
-  </si>
-  <si>
-    <t>=F5*50%</t>
-  </si>
-  <si>
-    <t>=F5*0,5</t>
-  </si>
-  <si>
-    <t>Potenciação</t>
-  </si>
-  <si>
-    <t>Elevo um número a outro</t>
-  </si>
-  <si>
-    <t>2²</t>
-  </si>
-  <si>
-    <t>3³</t>
-  </si>
-  <si>
-    <t>=H4^I4</t>
-  </si>
-  <si>
-    <t>=M25^O33</t>
-  </si>
-  <si>
-    <t>Altura</t>
-  </si>
-  <si>
-    <t>Peso</t>
-  </si>
-  <si>
-    <t>IMC</t>
-  </si>
-  <si>
-    <t>IMC2</t>
-  </si>
-  <si>
-    <t>Seu sexo</t>
-  </si>
-  <si>
-    <t>Seu nome</t>
-  </si>
-  <si>
-    <t>Sua data nascimento</t>
-  </si>
-  <si>
-    <t>Um salário</t>
-  </si>
-  <si>
-    <t>=E4+F4</t>
-  </si>
-  <si>
-    <t>=E5-F5</t>
-  </si>
-  <si>
-    <t>=E6*F6</t>
-  </si>
-  <si>
-    <t>=E7/F7</t>
-  </si>
-  <si>
-    <t>=E3=F3</t>
-  </si>
-  <si>
-    <t>=E4&gt;F4</t>
-  </si>
-  <si>
-    <t>=E6&gt;=F6</t>
-  </si>
-  <si>
-    <t>=E5&lt;F5</t>
-  </si>
-  <si>
-    <t>=E7&lt;=F7</t>
-  </si>
-  <si>
-    <t>=E8&lt;&gt;F8</t>
+    <t>Wagner Cesar Vieira</t>
+  </si>
+  <si>
+    <t>=(HOJE()-D4)/365,25</t>
+  </si>
+  <si>
+    <t>=ANO(HOJE())-ANO(D4)</t>
+  </si>
+  <si>
+    <t>=DATADIF(HOJE();D4;"Y")</t>
+  </si>
+  <si>
+    <t>=DATADIF(HOJE();D4;"YM")</t>
+  </si>
+  <si>
+    <t>=DATADIF(HOJE();D4;"MD")</t>
+  </si>
+  <si>
+    <t>Descontos (14%)</t>
+  </si>
+  <si>
+    <t>=J4*14%</t>
+  </si>
+  <si>
+    <t>=J4-K4</t>
   </si>
 </sst>
 </file>
@@ -430,7 +345,7 @@
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -516,13 +431,6 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="9" tint="-0.249977111117893"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -536,20 +444,44 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="8"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
+      <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="6"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="6"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="7" tint="-0.249977111117893"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="5"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF7030A0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -574,8 +506,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF66"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="20">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -776,69 +714,6 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -852,7 +727,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -901,13 +776,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="10" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -947,10 +816,10 @@
     <xf numFmtId="44" fontId="11" fillId="3" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -962,18 +831,12 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="44" fontId="10" fillId="0" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="11" fillId="0" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="3" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -992,9 +855,6 @@
     <xf numFmtId="44" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1004,13 +864,13 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="15" fillId="3" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="15" fillId="4" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="14" fillId="3" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="14" fillId="4" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="3" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1019,53 +879,92 @@
     <xf numFmtId="44" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="10" fillId="5" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="5" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="3" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="3" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1084,69 +983,6 @@
     </xf>
     <xf numFmtId="49" fontId="4" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="12" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="12" fillId="3" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="12" fillId="3" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1158,6 +994,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFFF66"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1728,43 +1569,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="84" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
+      <c r="B1" s="84"/>
+      <c r="C1" s="84"/>
+      <c r="D1" s="84"/>
+      <c r="E1" s="84"/>
+      <c r="F1" s="84"/>
+      <c r="G1" s="84"/>
     </row>
     <row r="2" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
+      <c r="A2" s="85"/>
+      <c r="B2" s="85"/>
+      <c r="C2" s="85"/>
       <c r="D2" s="4"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
+      <c r="E2" s="86"/>
+      <c r="F2" s="86"/>
+      <c r="G2" s="86"/>
     </row>
     <row r="3" spans="1:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="C3" s="26" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="4"/>
-      <c r="E3" s="29" t="s">
+      <c r="E3" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="30" t="s">
+      <c r="F3" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="31" t="s">
+      <c r="G3" s="29" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1775,7 +1616,7 @@
       <c r="B4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="34" t="s">
+      <c r="C4" s="32" t="s">
         <v>37</v>
       </c>
       <c r="D4" s="4"/>
@@ -1785,7 +1626,7 @@
       <c r="F4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="34" t="s">
+      <c r="G4" s="32" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1796,7 +1637,7 @@
       <c r="B5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="34" t="s">
+      <c r="C5" s="32" t="s">
         <v>38</v>
       </c>
       <c r="D5" s="4"/>
@@ -1806,7 +1647,7 @@
       <c r="F5" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="34" t="s">
+      <c r="G5" s="32" t="s">
         <v>52</v>
       </c>
     </row>
@@ -1817,7 +1658,7 @@
       <c r="B6" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="34" t="s">
+      <c r="C6" s="32" t="s">
         <v>39</v>
       </c>
       <c r="D6" s="4"/>
@@ -1827,7 +1668,7 @@
       <c r="F6" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G6" s="34" t="s">
+      <c r="G6" s="32" t="s">
         <v>53</v>
       </c>
     </row>
@@ -1838,7 +1679,7 @@
       <c r="B7" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="34" t="s">
+      <c r="C7" s="32" t="s">
         <v>40</v>
       </c>
       <c r="D7" s="4"/>
@@ -1848,7 +1689,7 @@
       <c r="F7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="34" t="s">
+      <c r="G7" s="32" t="s">
         <v>54</v>
       </c>
     </row>
@@ -1859,7 +1700,7 @@
       <c r="B8" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" s="32" t="s">
         <v>41</v>
       </c>
       <c r="D8" s="4"/>
@@ -1869,7 +1710,7 @@
       <c r="F8" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="34" t="s">
+      <c r="G8" s="32" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1880,7 +1721,7 @@
       <c r="B9" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="35" t="s">
+      <c r="C9" s="33" t="s">
         <v>42</v>
       </c>
       <c r="D9" s="4"/>
@@ -1890,7 +1731,7 @@
       <c r="F9" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="35" t="s">
+      <c r="G9" s="33" t="s">
         <v>56</v>
       </c>
     </row>
@@ -1900,15 +1741,15 @@
       <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="29" t="s">
+      <c r="A11" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="79" t="s">
+      <c r="B11" s="87" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="79"/>
-      <c r="D11" s="32"/>
-      <c r="E11" s="31" t="s">
+      <c r="C11" s="87"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="29" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1916,10 +1757,10 @@
       <c r="A12" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="74" t="s">
+      <c r="B12" s="82" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="74"/>
+      <c r="C12" s="82"/>
       <c r="D12" s="11"/>
       <c r="E12" s="7" t="s">
         <v>57</v>
@@ -1929,10 +1770,10 @@
       <c r="A13" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="74" t="s">
+      <c r="B13" s="82" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="74"/>
+      <c r="C13" s="82"/>
       <c r="D13" s="11"/>
       <c r="E13" s="7" t="s">
         <v>58</v>
@@ -1942,10 +1783,10 @@
       <c r="A14" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="75" t="s">
+      <c r="B14" s="83" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="75"/>
+      <c r="C14" s="83"/>
       <c r="D14" s="12"/>
       <c r="E14" s="10" t="s">
         <v>59</v>
@@ -2020,996 +1861,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7448C247-F0B6-41B9-B009-9EEC7A6C8679}">
-  <dimension ref="B2:Q33"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="2.5703125" style="16" customWidth="1"/>
-    <col min="2" max="2" width="36" style="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.28515625" style="16" customWidth="1"/>
-    <col min="4" max="4" width="24.5703125" style="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.85546875" style="16" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" style="16" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="9" style="16" customWidth="1"/>
-    <col min="10" max="10" width="18.140625" style="16" customWidth="1"/>
-    <col min="11" max="11" width="17.140625" style="16" customWidth="1"/>
-    <col min="12" max="12" width="17.7109375" style="16" customWidth="1"/>
-    <col min="13" max="13" width="20" style="16" customWidth="1"/>
-    <col min="14" max="14" width="13.5703125" style="16" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="16"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="86" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" s="87"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="82" t="s">
-        <v>60</v>
-      </c>
-      <c r="F2" s="84"/>
-      <c r="G2" s="84"/>
-      <c r="H2" s="84"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="90"/>
-      <c r="L2" s="91"/>
-      <c r="M2" s="80" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="3" spans="2:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="H3" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="I3" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="J3" s="55" t="s">
-        <v>61</v>
-      </c>
-      <c r="K3" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="L3" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="M3" s="81"/>
-    </row>
-    <row r="4" spans="2:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="49" t="s">
-        <v>113</v>
-      </c>
-      <c r="C4" s="37" t="s">
-        <v>112</v>
-      </c>
-      <c r="D4" s="58" t="s">
-        <v>114</v>
-      </c>
-      <c r="E4" s="59"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
-      <c r="J4" s="37" t="s">
-        <v>115</v>
-      </c>
-      <c r="K4" s="39"/>
-      <c r="L4" s="37"/>
-      <c r="M4" s="38"/>
-    </row>
-    <row r="5" spans="2:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="44" t="s">
-        <v>62</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="D5" s="46">
-        <v>34679</v>
-      </c>
-      <c r="E5" s="100"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="53">
-        <v>5571</v>
-      </c>
-      <c r="K5" s="42"/>
-      <c r="L5" s="17"/>
-      <c r="M5" s="25"/>
-    </row>
-    <row r="6" spans="2:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="43" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="36" t="s">
-        <v>71</v>
-      </c>
-      <c r="D6" s="47">
-        <v>38404</v>
-      </c>
-      <c r="E6" s="59"/>
-      <c r="F6" s="37"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="36"/>
-      <c r="J6" s="54">
-        <v>5009</v>
-      </c>
-      <c r="K6" s="39"/>
-      <c r="L6" s="37"/>
-      <c r="M6" s="38"/>
-    </row>
-    <row r="7" spans="2:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="C7" s="52" t="s">
-        <v>70</v>
-      </c>
-      <c r="D7" s="46">
-        <v>36581</v>
-      </c>
-      <c r="E7" s="100"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="42"/>
-      <c r="I7" s="42"/>
-      <c r="J7" s="53">
-        <v>2844</v>
-      </c>
-      <c r="K7" s="42"/>
-      <c r="L7" s="56"/>
-      <c r="M7" s="33"/>
-    </row>
-    <row r="8" spans="2:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="43" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" s="36" t="s">
-        <v>71</v>
-      </c>
-      <c r="D8" s="47">
-        <v>36211</v>
-      </c>
-      <c r="E8" s="59"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="39"/>
-      <c r="J8" s="54">
-        <v>4064</v>
-      </c>
-      <c r="K8" s="39"/>
-      <c r="L8" s="57"/>
-      <c r="M8" s="41"/>
-    </row>
-    <row r="9" spans="2:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="44" t="s">
-        <v>72</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" s="46">
-        <v>32082</v>
-      </c>
-      <c r="E9" s="100"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="42"/>
-      <c r="I9" s="42"/>
-      <c r="J9" s="53">
-        <v>5659</v>
-      </c>
-      <c r="K9" s="42"/>
-      <c r="L9" s="56"/>
-      <c r="M9" s="33"/>
-    </row>
-    <row r="10" spans="2:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="43" t="s">
-        <v>73</v>
-      </c>
-      <c r="C10" s="36" t="s">
-        <v>71</v>
-      </c>
-      <c r="D10" s="50">
-        <v>33663</v>
-      </c>
-      <c r="E10" s="59"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="39"/>
-      <c r="H10" s="39"/>
-      <c r="I10" s="39"/>
-      <c r="J10" s="54">
-        <v>3127</v>
-      </c>
-      <c r="K10" s="39"/>
-      <c r="L10" s="57"/>
-      <c r="M10" s="41"/>
-    </row>
-    <row r="11" spans="2:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="44" t="s">
-        <v>74</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="D11" s="46">
-        <v>38241</v>
-      </c>
-      <c r="E11" s="100"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="42"/>
-      <c r="I11" s="42"/>
-      <c r="J11" s="53">
-        <v>4122</v>
-      </c>
-      <c r="K11" s="42"/>
-      <c r="L11" s="56"/>
-      <c r="M11" s="33"/>
-    </row>
-    <row r="12" spans="2:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="43" t="s">
-        <v>75</v>
-      </c>
-      <c r="C12" s="36" t="s">
-        <v>71</v>
-      </c>
-      <c r="D12" s="47">
-        <v>38408</v>
-      </c>
-      <c r="E12" s="59"/>
-      <c r="F12" s="37"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="54">
-        <v>5356</v>
-      </c>
-      <c r="K12" s="39"/>
-      <c r="L12" s="40"/>
-      <c r="M12" s="41"/>
-    </row>
-    <row r="13" spans="2:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="100"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="48"/>
-      <c r="H13" s="48"/>
-      <c r="I13" s="48"/>
-      <c r="J13" s="48"/>
-      <c r="K13" s="42"/>
-      <c r="L13" s="48"/>
-      <c r="M13" s="48"/>
-    </row>
-    <row r="14" spans="2:13" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="2:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="51" t="s">
-        <v>31</v>
-      </c>
-      <c r="D15" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="92"/>
-      <c r="H15" s="92"/>
-      <c r="I15" s="92"/>
-      <c r="J15" s="20"/>
-      <c r="K15" s="93" t="s">
-        <v>84</v>
-      </c>
-      <c r="L15" s="94"/>
-      <c r="M15" s="19"/>
-    </row>
-    <row r="16" spans="2:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="51" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="92"/>
-      <c r="H16" s="92"/>
-      <c r="I16" s="92"/>
-      <c r="J16" s="20"/>
-      <c r="K16" s="93" t="s">
-        <v>85</v>
-      </c>
-      <c r="L16" s="94"/>
-      <c r="M16" s="19"/>
-    </row>
-    <row r="17" spans="2:17" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="D17" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="92"/>
-      <c r="H17" s="92"/>
-      <c r="I17" s="92"/>
-      <c r="J17" s="20"/>
-      <c r="K17" s="82"/>
-      <c r="L17" s="83"/>
-      <c r="M17" s="21"/>
-    </row>
-    <row r="18" spans="2:17" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="51" t="s">
-        <v>34</v>
-      </c>
-      <c r="K18" s="82" t="s">
-        <v>87</v>
-      </c>
-      <c r="L18" s="83"/>
-      <c r="M18" s="21"/>
-    </row>
-    <row r="19" spans="2:17" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="51" t="s">
-        <v>35</v>
-      </c>
-      <c r="D19" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="85"/>
-      <c r="H19" s="85"/>
-      <c r="I19" s="85"/>
-      <c r="J19" s="20"/>
-      <c r="K19" s="82" t="s">
-        <v>86</v>
-      </c>
-      <c r="L19" s="83"/>
-      <c r="M19" s="21"/>
-    </row>
-    <row r="20" spans="2:17" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="D20" s="22" t="s">
-        <v>80</v>
-      </c>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="85"/>
-      <c r="H20" s="85"/>
-      <c r="I20" s="85"/>
-      <c r="J20" s="20"/>
-      <c r="K20" s="82" t="s">
-        <v>30</v>
-      </c>
-      <c r="L20" s="83"/>
-      <c r="M20" s="21"/>
-    </row>
-    <row r="21" spans="2:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D21" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="E21" s="22"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="85"/>
-      <c r="H21" s="85"/>
-      <c r="I21" s="85"/>
-    </row>
-    <row r="24" spans="2:17" ht="15" x14ac:dyDescent="0.25">
-      <c r="L24" s="23"/>
-      <c r="M24" s="13"/>
-      <c r="N24" s="13"/>
-      <c r="O24" s="23"/>
-      <c r="P24" s="23"/>
-      <c r="Q24" s="23"/>
-    </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="L25" s="23"/>
-      <c r="M25" s="14"/>
-      <c r="N25" s="14"/>
-      <c r="O25" s="14"/>
-      <c r="P25" s="23"/>
-      <c r="Q25" s="23"/>
-    </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="L26" s="23"/>
-      <c r="M26" s="14"/>
-      <c r="N26" s="14"/>
-      <c r="O26" s="14"/>
-      <c r="P26" s="23"/>
-      <c r="Q26" s="23"/>
-    </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="L27" s="23"/>
-      <c r="M27" s="14"/>
-      <c r="N27" s="14"/>
-      <c r="O27" s="14"/>
-      <c r="P27" s="23"/>
-      <c r="Q27" s="23"/>
-    </row>
-    <row r="28" spans="2:17" ht="15" x14ac:dyDescent="0.25">
-      <c r="L28" s="23"/>
-      <c r="M28" s="13"/>
-      <c r="N28" s="13"/>
-      <c r="O28" s="13"/>
-      <c r="P28" s="23"/>
-      <c r="Q28" s="23"/>
-    </row>
-    <row r="29" spans="2:17" ht="15" x14ac:dyDescent="0.25">
-      <c r="L29" s="23"/>
-      <c r="M29" s="13"/>
-      <c r="N29" s="13"/>
-      <c r="O29" s="13"/>
-      <c r="P29" s="23"/>
-      <c r="Q29" s="23"/>
-    </row>
-    <row r="30" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L30" s="23"/>
-      <c r="M30" s="23"/>
-      <c r="N30" s="24"/>
-      <c r="O30" s="24"/>
-      <c r="P30" s="24"/>
-      <c r="Q30" s="24"/>
-    </row>
-    <row r="31" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
-      <c r="N31" s="24"/>
-      <c r="O31" s="24"/>
-      <c r="P31" s="24"/>
-      <c r="Q31" s="24"/>
-    </row>
-    <row r="32" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L32" s="23"/>
-      <c r="M32" s="23"/>
-      <c r="N32" s="24"/>
-      <c r="O32" s="24"/>
-      <c r="P32" s="24"/>
-      <c r="Q32" s="24"/>
-    </row>
-    <row r="33" spans="12:17" x14ac:dyDescent="0.25">
-      <c r="L33" s="23"/>
-      <c r="M33" s="23"/>
-      <c r="N33" s="23"/>
-      <c r="O33" s="23"/>
-      <c r="P33" s="23"/>
-      <c r="Q33" s="23"/>
-    </row>
-  </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="E2:I2"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="K16:L16"/>
-  </mergeCells>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02F17102-8C90-41CF-B38E-562CC778EC63}">
-  <dimension ref="B2:G7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="23.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="17.140625" customWidth="1"/>
-    <col min="5" max="6" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="28" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="F3" s="28" t="s">
-        <v>93</v>
-      </c>
-      <c r="G3" s="28" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="34" t="s">
-        <v>116</v>
-      </c>
-      <c r="E4" s="60">
-        <v>1</v>
-      </c>
-      <c r="F4" s="60">
-        <v>2</v>
-      </c>
-      <c r="G4" s="60"/>
-    </row>
-    <row r="5" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="34" t="s">
-        <v>117</v>
-      </c>
-      <c r="E5" s="60">
-        <v>3</v>
-      </c>
-      <c r="F5" s="60">
-        <v>4</v>
-      </c>
-      <c r="G5" s="60"/>
-    </row>
-    <row r="6" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="34" t="s">
-        <v>118</v>
-      </c>
-      <c r="E6" s="60">
-        <v>5</v>
-      </c>
-      <c r="F6" s="60">
-        <v>6</v>
-      </c>
-      <c r="G6" s="60"/>
-    </row>
-    <row r="7" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="34" t="s">
-        <v>119</v>
-      </c>
-      <c r="E7" s="60">
-        <v>7</v>
-      </c>
-      <c r="F7" s="60">
-        <v>8</v>
-      </c>
-      <c r="G7" s="60"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="16" type="noConversion"/>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC9A1233-DDE2-4D1C-A5F5-82F567667EC3}">
-  <dimension ref="B1:G9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="4.42578125" customWidth="1"/>
-    <col min="2" max="2" width="46.85546875" customWidth="1"/>
-    <col min="3" max="3" width="21.28515625" customWidth="1"/>
-    <col min="4" max="4" width="16.7109375" customWidth="1"/>
-    <col min="5" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="61" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="71" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="72" t="s">
-        <v>92</v>
-      </c>
-      <c r="F2" s="72" t="s">
-        <v>95</v>
-      </c>
-      <c r="G2" s="70" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="3" spans="2:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C3" s="62" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="65" t="s">
-        <v>120</v>
-      </c>
-      <c r="E3" s="64">
-        <v>0</v>
-      </c>
-      <c r="F3" s="64">
-        <v>5</v>
-      </c>
-      <c r="G3" s="66"/>
-    </row>
-    <row r="4" spans="2:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="62" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="65" t="s">
-        <v>121</v>
-      </c>
-      <c r="E4" s="64">
-        <v>1</v>
-      </c>
-      <c r="F4" s="64">
-        <v>4</v>
-      </c>
-      <c r="G4" s="66"/>
-    </row>
-    <row r="5" spans="2:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C5" s="62" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="65" t="s">
-        <v>123</v>
-      </c>
-      <c r="E5" s="64">
-        <v>2</v>
-      </c>
-      <c r="F5" s="64">
-        <v>3</v>
-      </c>
-      <c r="G5" s="66"/>
-    </row>
-    <row r="6" spans="2:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" s="62" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="65" t="s">
-        <v>122</v>
-      </c>
-      <c r="E6" s="64">
-        <v>3</v>
-      </c>
-      <c r="F6" s="64">
-        <v>2</v>
-      </c>
-      <c r="G6" s="66"/>
-    </row>
-    <row r="7" spans="2:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" s="62" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="65" t="s">
-        <v>124</v>
-      </c>
-      <c r="E7" s="64">
-        <v>4</v>
-      </c>
-      <c r="F7" s="64">
-        <v>1</v>
-      </c>
-      <c r="G7" s="66"/>
-    </row>
-    <row r="8" spans="2:7" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C8" s="63" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="67" t="s">
-        <v>125</v>
-      </c>
-      <c r="E8" s="68">
-        <v>5</v>
-      </c>
-      <c r="F8" s="68">
-        <v>0</v>
-      </c>
-      <c r="G8" s="69"/>
-    </row>
-    <row r="9" spans="2:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25"/>
-  </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6208FAE-9324-4490-9E06-50B700988D92}">
-  <dimension ref="B4:H9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="24.42578125" customWidth="1"/>
-    <col min="3" max="3" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.85546875" customWidth="1"/>
-    <col min="5" max="5" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="4" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="5" spans="2:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="26" t="s">
-        <v>96</v>
-      </c>
-      <c r="C5" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="28" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="F5" s="28" t="s">
-        <v>93</v>
-      </c>
-      <c r="G5" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="H5" s="28" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="6" spans="2:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C6" s="95" t="s">
-        <v>99</v>
-      </c>
-      <c r="D6" s="98" t="s">
-        <v>100</v>
-      </c>
-      <c r="E6" s="60">
-        <v>10</v>
-      </c>
-      <c r="F6" s="60">
-        <v>50</v>
-      </c>
-      <c r="G6" s="60"/>
-      <c r="H6" s="60"/>
-    </row>
-    <row r="7" spans="2:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="96"/>
-      <c r="D7" s="99"/>
-      <c r="E7" s="60">
-        <v>20</v>
-      </c>
-      <c r="F7" s="60">
-        <v>60</v>
-      </c>
-      <c r="G7" s="60"/>
-      <c r="H7" s="60"/>
-    </row>
-    <row r="8" spans="2:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C8" s="96"/>
-      <c r="D8" s="98" t="s">
-        <v>101</v>
-      </c>
-      <c r="E8" s="60">
-        <v>30</v>
-      </c>
-      <c r="F8" s="60">
-        <v>70</v>
-      </c>
-      <c r="G8" s="60"/>
-      <c r="H8" s="60"/>
-    </row>
-    <row r="9" spans="2:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C9" s="97"/>
-      <c r="D9" s="99"/>
-      <c r="E9" s="60">
-        <v>40</v>
-      </c>
-      <c r="F9" s="60">
-        <v>80</v>
-      </c>
-      <c r="G9" s="60"/>
-      <c r="H9" s="60"/>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="C6:C9"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="D8:D9"/>
-  </mergeCells>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FED641B-6E1F-4E18-8337-96240CD3630C}">
-  <dimension ref="B2:H7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="3" width="18.42578125" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="2:8" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B3" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="28" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="28" t="s">
-        <v>108</v>
-      </c>
-      <c r="F3" s="28" t="s">
-        <v>109</v>
-      </c>
-      <c r="G3" s="28" t="s">
-        <v>110</v>
-      </c>
-      <c r="H3" s="28" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8" ht="18" x14ac:dyDescent="0.25">
-      <c r="B4" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C4" s="95" t="s">
-        <v>103</v>
-      </c>
-      <c r="D4" s="98" t="s">
-        <v>106</v>
-      </c>
-      <c r="E4" s="60">
-        <v>1.55</v>
-      </c>
-      <c r="F4" s="60">
-        <v>70</v>
-      </c>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-    </row>
-    <row r="5" spans="2:8" ht="18" x14ac:dyDescent="0.25">
-      <c r="B5" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C5" s="96"/>
-      <c r="D5" s="99"/>
-      <c r="E5" s="60">
-        <v>1.91</v>
-      </c>
-      <c r="F5" s="60">
-        <v>100</v>
-      </c>
-      <c r="G5" s="73"/>
-      <c r="H5" s="73"/>
-    </row>
-    <row r="6" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C6" s="96"/>
-      <c r="D6" s="98" t="s">
-        <v>107</v>
-      </c>
-      <c r="E6" s="60">
-        <v>1.82</v>
-      </c>
-      <c r="F6" s="60">
-        <v>50</v>
-      </c>
-      <c r="G6" s="73"/>
-      <c r="H6" s="73"/>
-    </row>
-    <row r="7" spans="2:8" ht="18" x14ac:dyDescent="0.25">
-      <c r="B7" s="6"/>
-      <c r="C7" s="97"/>
-      <c r="D7" s="99"/>
-      <c r="E7" s="60">
-        <v>1.65</v>
-      </c>
-      <c r="F7" s="60">
-        <v>32</v>
-      </c>
-      <c r="G7" s="73"/>
-      <c r="H7" s="73"/>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="C4:C7"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="D6:D7"/>
-  </mergeCells>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24BA2FE8-89DB-4B9A-9BE6-A5E8DDCA08A1}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3017,4 +1868,510 @@
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7448C247-F0B6-41B9-B009-9EEC7A6C8679}">
+  <dimension ref="B2:P33"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="2.5703125" style="16" customWidth="1"/>
+    <col min="2" max="2" width="36" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" style="16" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" style="16" customWidth="1"/>
+    <col min="5" max="5" width="24.7109375" style="16" customWidth="1"/>
+    <col min="6" max="6" width="27.42578125" style="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="31.28515625" style="16" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.140625" style="16" customWidth="1"/>
+    <col min="11" max="11" width="17.7109375" style="16" customWidth="1"/>
+    <col min="12" max="12" width="20" style="16" customWidth="1"/>
+    <col min="13" max="13" width="13.5703125" style="16" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="16"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="74" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="75"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="70" t="s">
+        <v>60</v>
+      </c>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="68" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" s="53" t="s">
+        <v>66</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="H3" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="J3" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="K3" s="56" t="s">
+        <v>96</v>
+      </c>
+      <c r="L3" s="69"/>
+    </row>
+    <row r="4" spans="2:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="57" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4" s="58" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" s="59">
+        <v>27443</v>
+      </c>
+      <c r="E4" s="60" t="s">
+        <v>91</v>
+      </c>
+      <c r="F4" s="61" t="s">
+        <v>92</v>
+      </c>
+      <c r="G4" s="62" t="s">
+        <v>93</v>
+      </c>
+      <c r="H4" s="63" t="s">
+        <v>94</v>
+      </c>
+      <c r="I4" s="64" t="s">
+        <v>95</v>
+      </c>
+      <c r="J4" s="65">
+        <v>4500</v>
+      </c>
+      <c r="K4" s="66" t="s">
+        <v>97</v>
+      </c>
+      <c r="L4" s="67" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="40" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" s="42">
+        <v>34679</v>
+      </c>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="48">
+        <v>5571</v>
+      </c>
+      <c r="K5" s="17"/>
+      <c r="L5" s="23"/>
+    </row>
+    <row r="6" spans="2:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" s="43">
+        <v>38404</v>
+      </c>
+      <c r="E6" s="35"/>
+      <c r="F6" s="35"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="34"/>
+      <c r="I6" s="34"/>
+      <c r="J6" s="49">
+        <v>5009</v>
+      </c>
+      <c r="K6" s="35"/>
+      <c r="L6" s="36"/>
+    </row>
+    <row r="7" spans="2:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="41" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="47" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" s="42">
+        <v>36581</v>
+      </c>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="54"/>
+      <c r="I7" s="54"/>
+      <c r="J7" s="48">
+        <v>2844</v>
+      </c>
+      <c r="K7" s="51"/>
+      <c r="L7" s="31"/>
+    </row>
+    <row r="8" spans="2:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="D8" s="43">
+        <v>36211</v>
+      </c>
+      <c r="E8" s="35"/>
+      <c r="F8" s="35"/>
+      <c r="G8" s="55"/>
+      <c r="H8" s="55"/>
+      <c r="I8" s="55"/>
+      <c r="J8" s="49">
+        <v>4064</v>
+      </c>
+      <c r="K8" s="52"/>
+      <c r="L8" s="38"/>
+    </row>
+    <row r="9" spans="2:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" s="42">
+        <v>32082</v>
+      </c>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="54"/>
+      <c r="I9" s="54"/>
+      <c r="J9" s="48">
+        <v>5659</v>
+      </c>
+      <c r="K9" s="51"/>
+      <c r="L9" s="31"/>
+    </row>
+    <row r="10" spans="2:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="D10" s="45">
+        <v>33663</v>
+      </c>
+      <c r="E10" s="35"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="55"/>
+      <c r="H10" s="55"/>
+      <c r="I10" s="55"/>
+      <c r="J10" s="49">
+        <v>3127</v>
+      </c>
+      <c r="K10" s="52"/>
+      <c r="L10" s="38"/>
+    </row>
+    <row r="11" spans="2:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="40" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="D11" s="42">
+        <v>38241</v>
+      </c>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="54"/>
+      <c r="I11" s="54"/>
+      <c r="J11" s="48">
+        <v>4122</v>
+      </c>
+      <c r="K11" s="51"/>
+      <c r="L11" s="31"/>
+    </row>
+    <row r="12" spans="2:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="D12" s="43">
+        <v>38408</v>
+      </c>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="55"/>
+      <c r="H12" s="55"/>
+      <c r="I12" s="55"/>
+      <c r="J12" s="49">
+        <v>5356</v>
+      </c>
+      <c r="K12" s="37"/>
+      <c r="L12" s="38"/>
+    </row>
+    <row r="13" spans="2:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="44"/>
+      <c r="K13" s="44"/>
+      <c r="L13" s="44"/>
+    </row>
+    <row r="14" spans="2:12" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="2:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="79"/>
+      <c r="H15" s="79"/>
+      <c r="I15" s="79"/>
+      <c r="J15" s="80" t="s">
+        <v>82</v>
+      </c>
+      <c r="K15" s="81"/>
+      <c r="L15" s="18"/>
+    </row>
+    <row r="16" spans="2:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="79"/>
+      <c r="H16" s="79"/>
+      <c r="I16" s="79"/>
+      <c r="J16" s="80" t="s">
+        <v>83</v>
+      </c>
+      <c r="K16" s="81"/>
+      <c r="L16" s="18"/>
+    </row>
+    <row r="17" spans="2:16" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="46" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="79"/>
+      <c r="H17" s="79"/>
+      <c r="I17" s="79"/>
+      <c r="J17" s="70"/>
+      <c r="K17" s="71"/>
+      <c r="L17" s="19"/>
+    </row>
+    <row r="18" spans="2:16" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="J18" s="70" t="s">
+        <v>85</v>
+      </c>
+      <c r="K18" s="71"/>
+      <c r="L18" s="19"/>
+    </row>
+    <row r="19" spans="2:16" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="46" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="73"/>
+      <c r="H19" s="73"/>
+      <c r="I19" s="73"/>
+      <c r="J19" s="70" t="s">
+        <v>84</v>
+      </c>
+      <c r="K19" s="71"/>
+      <c r="L19" s="19"/>
+    </row>
+    <row r="20" spans="2:16" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="73"/>
+      <c r="H20" s="73"/>
+      <c r="I20" s="73"/>
+      <c r="J20" s="70" t="s">
+        <v>30</v>
+      </c>
+      <c r="K20" s="71"/>
+      <c r="L20" s="19"/>
+    </row>
+    <row r="21" spans="2:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D21" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="73"/>
+      <c r="H21" s="73"/>
+      <c r="I21" s="73"/>
+    </row>
+    <row r="24" spans="2:16" ht="15" x14ac:dyDescent="0.25">
+      <c r="K24" s="21"/>
+      <c r="L24" s="13"/>
+      <c r="M24" s="13"/>
+      <c r="N24" s="21"/>
+      <c r="O24" s="21"/>
+      <c r="P24" s="21"/>
+    </row>
+    <row r="25" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K25" s="21"/>
+      <c r="L25" s="14"/>
+      <c r="M25" s="14"/>
+      <c r="N25" s="14"/>
+      <c r="O25" s="21"/>
+      <c r="P25" s="21"/>
+    </row>
+    <row r="26" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K26" s="21"/>
+      <c r="L26" s="14"/>
+      <c r="M26" s="14"/>
+      <c r="N26" s="14"/>
+      <c r="O26" s="21"/>
+      <c r="P26" s="21"/>
+    </row>
+    <row r="27" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K27" s="21"/>
+      <c r="L27" s="14"/>
+      <c r="M27" s="14"/>
+      <c r="N27" s="14"/>
+      <c r="O27" s="21"/>
+      <c r="P27" s="21"/>
+    </row>
+    <row r="28" spans="2:16" ht="15" x14ac:dyDescent="0.25">
+      <c r="K28" s="21"/>
+      <c r="L28" s="13"/>
+      <c r="M28" s="13"/>
+      <c r="N28" s="13"/>
+      <c r="O28" s="21"/>
+      <c r="P28" s="21"/>
+    </row>
+    <row r="29" spans="2:16" ht="15" x14ac:dyDescent="0.25">
+      <c r="K29" s="21"/>
+      <c r="L29" s="13"/>
+      <c r="M29" s="13"/>
+      <c r="N29" s="13"/>
+      <c r="O29" s="21"/>
+      <c r="P29" s="21"/>
+    </row>
+    <row r="30" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K30" s="21"/>
+      <c r="L30" s="21"/>
+      <c r="M30" s="22"/>
+      <c r="N30" s="22"/>
+      <c r="O30" s="22"/>
+      <c r="P30" s="22"/>
+    </row>
+    <row r="31" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K31" s="21"/>
+      <c r="L31" s="21"/>
+      <c r="M31" s="22"/>
+      <c r="N31" s="22"/>
+      <c r="O31" s="22"/>
+      <c r="P31" s="22"/>
+    </row>
+    <row r="32" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K32" s="21"/>
+      <c r="L32" s="21"/>
+      <c r="M32" s="22"/>
+      <c r="N32" s="22"/>
+      <c r="O32" s="22"/>
+      <c r="P32" s="22"/>
+    </row>
+    <row r="33" spans="11:16" x14ac:dyDescent="0.25">
+      <c r="K33" s="21"/>
+      <c r="L33" s="21"/>
+      <c r="M33" s="21"/>
+      <c r="N33" s="21"/>
+      <c r="O33" s="21"/>
+      <c r="P33" s="21"/>
+    </row>
+  </sheetData>
+  <protectedRanges>
+    <protectedRange algorithmName="SHA-512" hashValue="vqOWtweCAGcHSbISv8MhXSssMh50k9mmnKJ8+w+ipM1TQgkoXKEs7KFC7X9qSG/hlxWQFdLbHYbkpUYj2DT8CQ==" saltValue="nAURs2/Y/H/9GnMADEDFeQ==" spinCount="100000" sqref="B4:L4" name="Intervalo1"/>
+  </protectedRanges>
+  <mergeCells count="16">
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="E2:I2"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="J16:K16"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>